--- a/BA/Part 1_Stakeholder Analysis amp Management-20260912/Done/AI/Artifacts/4. Communication Plan_VNS.xlsx
+++ b/BA/Part 1_Stakeholder Analysis amp Management-20260912/Done/AI/Artifacts/4. Communication Plan_VNS.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>V1.1</t>
+          <t>V1.2</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
     <row r="11" ht="52" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Requirements Elicitation Meeting with the Customer</t>
+          <t>Requirements Elicitation Meeting with Lecturers</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Nataliia Boiko, BA; PO and Tech Lead as needed</t>
+          <t>End users — lecturers, BA; PO and Tech Lead as needed</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Validate prototypes with real students and collect pain points on deadlines, grade forecast and communication</t>
+          <t>Validate prototypes with students and lecturers and collect pain points on deadlines, grade forecast and communication</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>End users — Lviv Polytechnic students, BA, QA, PO</t>
+          <t>End users — students and lecturers, BA, QA, PO</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Discuss the custom backend architecture, the data model, technical debt and dependencies between modules</t>
+          <t>Discuss the custom backend architecture, the data model, deployment, technical debt and dependencies between modules</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Tech Lead, DevOps, QA, PM; BA as needed</t>
+          <t>Software engineers (Tech Lead, DevOps, QA), PM; BA as needed</t>
         </is>
       </c>
     </row>
@@ -855,22 +855,22 @@
     <row r="15" ht="52" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Coordination with the University Technical Department</t>
+          <t>Requests to the University Technical Department</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Working meeting + e-mail</t>
+          <t>E-mail / ticket</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Every two weeks</t>
+          <t>As needed (registry export, infrastructure access)</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Agree access to the student registry, infrastructure, domain, certificates and the security policy</t>
+          <t>Request the export of the student registry and access to university infrastructure, domain and certificates</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Technical Department of Lviv Polytechnic, DevOps, Tech Lead, PM</t>
+          <t>Technical Department of Lviv Polytechnic, DevOps, Tech Lead</t>
         </is>
       </c>
     </row>
@@ -912,14 +912,14 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Lviv Polytechnic National University, Nataliia Boiko, PM, PO, BA</t>
+          <t>Lviv Polytechnic National University, PM, PO, BA</t>
         </is>
       </c>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Increment Demo for the Customer</t>
+          <t>Increment Demo for the Sponsor and End Users</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Nataliia Boiko, PO, PM, BA, QA</t>
+          <t>Lviv Polytechnic National University, end-user representatives, PO, PM, BA, QA</t>
         </is>
       </c>
     </row>
@@ -1008,19 +1008,19 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>PO, PM, BA, Tech Lead; Nataliia Boiko for material changes</t>
+          <t>PO, PM, BA, Tech Lead; the sponsor for material changes</t>
         </is>
       </c>
     </row>
     <row r="20" ht="52" customHeight="1">
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Summary for the Rector's Office</t>
+          <t>Semester Report to the Ministry of Education and Science</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>E-mail with a one-page summary</t>
+          <t>Official one-page report</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Report status, pilot results and the decision needed on scaling the product across the university</t>
+          <t>Keep the regulator satisfied: report progress, pilot results and compliance with personal-data and educational IT regulation</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Nataliia Shakhovska (Rector), Lviv Polytechnic National University, PM</t>
+          <t>Ministry of Education and Science of Ukraine, Lviv Polytechnic National University, PM</t>
         </is>
       </c>
     </row>

--- a/BA/Part 1_Stakeholder Analysis amp Management-20260912/Done/AI/Artifacts/4. Communication Plan_VNS.xlsx
+++ b/BA/Part 1_Stakeholder Analysis amp Management-20260912/Done/AI/Artifacts/4. Communication Plan_VNS.xlsx
@@ -89,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -136,6 +136,17 @@
       <right style="thin">
         <color rgb="00B4C6E7"/>
       </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="00B4C6E7"/>
       </top>
@@ -543,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G35"/>
+  <dimension ref="A2:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -573,6 +584,7 @@
           <t>Initiation</t>
         </is>
       </c>
+      <c r="D4" s="8" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Date</t>
@@ -583,6 +595,7 @@
           <t>02/10/2026</t>
         </is>
       </c>
+      <c r="G4" s="8" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="2" t="inlineStr">
@@ -595,6 +608,7 @@
           <t>Nazar Zankovych, Project Manager</t>
         </is>
       </c>
+      <c r="D5" s="8" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Version</t>
@@ -605,6 +619,7 @@
           <t>V1.2</t>
         </is>
       </c>
+      <c r="G5" s="8" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="B6" s="2" t="inlineStr">
@@ -617,6 +632,7 @@
           <t>English for documentation; Ukrainian for day-to-day team work</t>
         </is>
       </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Validity period</t>
@@ -627,6 +643,7 @@
           <t>22/09/2026 – 31/01/2027</t>
         </is>
       </c>
+      <c r="G6" s="8" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="B8" s="4" t="inlineStr">
@@ -1044,232 +1061,56 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>COMMUNICATION ESCALATION PROCESS</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>Decision Authority</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Timeframe for Resolution</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="n"/>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Priority 1</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Major impact: the team is blocked, or the pilot or project deadline is at risk</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Lviv Polytechnic National University (Sponsor)</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Within 1 business day</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Priority 2</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Medium impact: individual activities or the MVP scope may slip</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>Product Owner</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>Within 2 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>Priority 3</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Slight impact: minor scheduling difficulties with no effect on scope or outcome</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Within 3 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Priority 4</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>No impact on the project, but a better solution may exist</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Handled through the change management process</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>COMMUNICATION STANDARDS</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>Meeting agenda</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Distributed to participants no later than 2 business days before the meeting; identifies the topics, the presenter and a time limit for each. The first item is always a review of action items from the previous meeting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>Meeting minutes</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Published within 1 business day after the meeting; contain the decisions taken, new action items with a named owner and due date, and the Parking Lot list.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>Channels</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Formal documents and approvals — university @lpnu.ua mailboxes. Day-to-day team work — team chat. Tasks and defects — issue tracker.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>Confidentiality</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Personal data of students and lecturers is not distributed through external channels. Any transfer of course materials to the external LLM API is approved by Lviv Polytechnic National University as the owner of the data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>Escalation rule</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Issues involving personal data or the transfer of materials to the external LLM API are escalated to the sponsor regardless of the priority assigned.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>Link to the register</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>The frequency and method of each communication match the “Preferable way of communication” and “Frequency of Communication” columns in “1. Stakeholder Register_VNS.xlsx”.</t>
-        </is>
-      </c>
-    </row>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
   </sheetData>
   <autoFilter ref="B8:G20"/>
-  <mergeCells count="25">
+  <mergeCells count="7">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="F4:G4"/>
-    <mergeCell ref="C30:G30"/>
     <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="F25:G25"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C33:G33"/>
     <mergeCell ref="F6:G6"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="B29:G29"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="C25:D25"/>
     <mergeCell ref="F5:G5"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="C32:G32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
